--- a/accountant-skill/data/output/May2025/trial_balance_May2025.xlsx
+++ b/accountant-skill/data/output/May2025/trial_balance_May2025.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dr: 744,083,780.36 | Cr: 745,297,479.29</t>
+          <t>Dr: 1,212,945,241.67 | Cr: 1,214,158,940.60</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dr: 861,876,702.49 | Cr: 863,090,401.42</t>
+          <t>Dr: 1,335,158,957.25 | Cr: 1,336,372,656.18</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2606894.92</v>
+        <v>8212071.920000004</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>5597336.1</v>
@@ -658,7 +658,7 @@
         <v>8212072.36</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7841.340000000782</v>
+        <v>5597335.660000003</v>
       </c>
     </row>
     <row r="9">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>15956051</v>
+        <v>23855351</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>22235468.71</v>
@@ -680,7 +680,7 @@
         <v>23855351</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>14336168.71</v>
+        <v>22235468.71</v>
       </c>
     </row>
     <row r="10">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4704661.689999998</v>
+        <v>29756984.31</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>34185619.1</v>
@@ -702,7 +702,7 @@
         <v>29756984.31</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>276026.8999999948</v>
+        <v>34185619.10000001</v>
       </c>
     </row>
     <row r="11">
@@ -771,12 +771,12 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>210290000</v>
+        <v>429290000</v>
       </c>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="n">
-        <v>210290000</v>
+        <v>429290000</v>
       </c>
     </row>
     <row r="16">
@@ -788,10 +788,14 @@
           <t>Buildings &amp; Structures</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n"/>
+      <c r="C16" s="4" t="n">
+        <v>133000000</v>
+      </c>
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
+      <c r="F16" s="4" t="n">
+        <v>133000000</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -803,14 +807,14 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1662500.01</v>
+        <v>21612500.01000001</v>
       </c>
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n">
         <v>554166.67</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2216666.68</v>
+        <v>22166666.68000001</v>
       </c>
     </row>
     <row r="18">
@@ -823,12 +827,12 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1520000</v>
+        <v>67920000</v>
       </c>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n">
-        <v>1520000</v>
+        <v>67920000</v>
       </c>
     </row>
     <row r="19">
@@ -841,14 +845,14 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2528334.33</v>
+        <v>14903634.33</v>
       </c>
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n">
         <v>1767212</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4295546.33</v>
+        <v>16670846.33</v>
       </c>
     </row>
     <row r="20">
@@ -889,12 +893,12 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>6856000</v>
+        <v>14056000</v>
       </c>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n">
-        <v>6856000</v>
+        <v>14056000</v>
       </c>
     </row>
     <row r="23">
@@ -907,14 +911,14 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>558595.3300000001</v>
+        <v>2268595.33</v>
       </c>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n">
         <v>392913</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>951508.3300000001</v>
+        <v>2661508.33</v>
       </c>
     </row>
     <row r="24">
@@ -1059,12 +1063,12 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>400000000</v>
+        <v>839530823</v>
       </c>
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n">
-        <v>400000000</v>
+        <v>839530823</v>
       </c>
     </row>
     <row r="34">
@@ -1613,7 +1617,7 @@
       </c>
       <c r="B65" s="6" t="n"/>
       <c r="C65" s="7" t="n">
-        <v>745297479.2900001</v>
+        <v>1214158940.6</v>
       </c>
       <c r="D65" s="7" t="n">
         <v>271917593.2500001</v>
@@ -1622,7 +1626,7 @@
         <v>271917593.25</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>863090401.4200001</v>
+        <v>1336372656.18</v>
       </c>
     </row>
   </sheetData>
